--- a/output/daily_screen_20260929.xlsx
+++ b/output/daily_screen_20260929.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -703,7 +703,7 @@
         <v>6895</v>
       </c>
       <c r="R2" t="n">
-        <v>1655929</v>
+        <v>1591830</v>
       </c>
       <c r="S2" t="n">
         <v>6369</v>
@@ -739,13 +739,13 @@
         <v>1.02859958568814</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1472997259097635</v>
+        <v>0.1638058005062069</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.007212199059683</v>
+        <v>1.009606822136877</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.8599124731499193</v>
+        <v>-0.8458010216306706</v>
       </c>
       <c r="AG2" t="n">
         <v>92</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -845,7 +845,7 @@
         <v>1270</v>
       </c>
       <c r="R3" t="n">
-        <v>9198391</v>
+        <v>8867403</v>
       </c>
       <c r="S3" t="n">
         <v>1189</v>
@@ -881,13 +881,13 @@
         <v>0.07172995780590719</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.02038226589328662</v>
+        <v>-0.003876191296843245</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05034257117744989</v>
+        <v>0.05273719425464463</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07072483707073651</v>
+        <v>-0.05661338555148787</v>
       </c>
       <c r="AG3" t="n">
         <v>54</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>80.60000000000001</v>
+        <v>80.80000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -987,7 +987,7 @@
         <v>2445</v>
       </c>
       <c r="R4" t="n">
-        <v>4550271</v>
+        <v>4308131</v>
       </c>
       <c r="S4" t="n">
         <v>2334</v>
@@ -1023,13 +1023,13 @@
         <v>0.2363031465504604</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0372825927992626</v>
+        <v>0.05378866739570598</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2149157599220031</v>
+        <v>0.2173103829991978</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1776331671227405</v>
+        <v>-0.1635217156034918</v>
       </c>
       <c r="AG4" t="n">
         <v>74</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1129,7 +1129,7 @@
         <v>178.5</v>
       </c>
       <c r="R5" t="n">
-        <v>34211681</v>
+        <v>33763957</v>
       </c>
       <c r="S5" t="n">
         <v>173.4</v>
@@ -1165,13 +1165,13 @@
         <v>-0.05568660955828064</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1220908523862834</v>
+        <v>0.1385969269827267</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.07707399618673794</v>
+        <v>-0.0746793731095432</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1991648485730213</v>
+        <v>0.2132763000922699</v>
       </c>
       <c r="AG5" t="n">
         <v>86</v>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71.2</v>
+        <v>78</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,15 +1239,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3483000</v>
+        <v>2674000</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3483000</v>
+        <v>2674000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1265,61 +1265,61 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>498.5</v>
+        <v>216</v>
       </c>
       <c r="Q6" t="n">
-        <v>498.5</v>
+        <v>216</v>
       </c>
       <c r="R6" t="n">
-        <v>41882089</v>
+        <v>11046647</v>
       </c>
       <c r="S6" t="n">
-        <v>481.2</v>
+        <v>209</v>
       </c>
       <c r="T6" t="n">
-        <v>489.1</v>
+        <v>195.975</v>
       </c>
       <c r="U6" t="n">
-        <v>488.2</v>
+        <v>195.25</v>
       </c>
       <c r="V6" t="n">
-        <v>493.4</v>
+        <v>179.7979118347168</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1396022943689559</v>
+        <v>6.658701056388509</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007145187042290509</v>
+        <v>3.766365760948625</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1388877756647268</v>
+        <v>2.892335295439884</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.202645883787668</v>
+        <v>2.605450449051671</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03746097814776284</v>
+        <v>0.07196029776674928</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1867862969004894</v>
+        <v>0.04802908408167728</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.007114836132620539</v>
+        <v>0.04389055808280928</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2081736835289467</v>
+        <v>0.02903632053041472</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2010588473963262</v>
+        <v>0.01485423755239457</v>
       </c>
       <c r="AG6" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="AI6" t="b">
         <v>1</v>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1372,96 +1372,96 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2674000</v>
+        <v>3483000</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3483000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>40884370</v>
+      </c>
+      <c r="S7" t="n">
+        <v>481.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>489.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>488.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>493.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1396022943689559</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.0007145187042290509</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1388877756647268</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2.202645883787668</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.03746097814776284</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.1867862969004894</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.009391238463822837</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.205779060451752</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2151702989155748</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AH7" t="n">
         <v>20</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3193000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-519000</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.1625430629502036</v>
-      </c>
-      <c r="P7" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>216</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11282373</v>
-      </c>
-      <c r="S7" t="n">
-        <v>209</v>
-      </c>
-      <c r="T7" t="n">
-        <v>195.975</v>
-      </c>
-      <c r="U7" t="n">
-        <v>195.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>179.7979118347168</v>
-      </c>
-      <c r="W7" t="n">
-        <v>6.658701056388509</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.766365760948625</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.892335295439884</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.605450449051671</v>
-      </c>
-      <c r="AA7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.07196029776674928</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.04802908408167728</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.02738448348636591</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.02664169745321998</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.0007427860331459257</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>68</v>
       </c>
       <c r="AI7" t="b">
         <v>1</v>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47.40000000000001</v>
+        <v>45.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,15 +1523,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>121000</v>
+        <v>2483000</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -1540,70 +1540,70 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1000</v>
+        <v>2022000</v>
       </c>
       <c r="N8" t="n">
-        <v>120000</v>
+        <v>461000</v>
       </c>
       <c r="O8" t="n">
-        <v>120</v>
+        <v>0.2279920870425322</v>
       </c>
       <c r="P8" t="n">
-        <v>1310</v>
+        <v>1120</v>
       </c>
       <c r="Q8" t="n">
-        <v>1310</v>
+        <v>1120</v>
       </c>
       <c r="R8" t="n">
-        <v>3497503</v>
+        <v>8611300</v>
       </c>
       <c r="S8" t="n">
-        <v>1232</v>
+        <v>1090</v>
       </c>
       <c r="T8" t="n">
-        <v>1278</v>
+        <v>1074.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1280.75</v>
+        <v>1074.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1157.184970092773</v>
+        <v>1010.283333333333</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.482500372270351</v>
+        <v>15.44991409719159</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.492960901690422</v>
+        <v>2.798912882849386</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01046052942007059</v>
+        <v>12.65100121434221</v>
       </c>
       <c r="Z8" t="n">
-        <v>-11.81469275014517</v>
+        <v>10.5978825348422</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.04029304029304026</v>
+        <v>-0.008849557522123908</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2880115114876634</v>
+        <v>-0.1417624521072797</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.08486885457342364</v>
+        <v>-0.03691929720606391</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.2666241248592061</v>
+        <v>-0.1607552156585422</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.3514929794326297</v>
+        <v>0.1238359184524783</v>
       </c>
       <c r="AG8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AH8" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="b">
         <v>1</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>1311.32</v>
+        <v>1116.79</v>
       </c>
     </row>
     <row r="9">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1654,24 +1654,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45.8</v>
+        <v>38.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2022000</v>
+        <v>121000</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1680,70 +1680,70 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1634000</v>
+        <v>121000</v>
       </c>
       <c r="N9" t="n">
-        <v>388000</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2374541003671971</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1120</v>
+        <v>1310</v>
       </c>
       <c r="Q9" t="n">
-        <v>1120</v>
+        <v>1310</v>
       </c>
       <c r="R9" t="n">
-        <v>8798725</v>
+        <v>3324760</v>
       </c>
       <c r="S9" t="n">
-        <v>1090</v>
+        <v>1232</v>
       </c>
       <c r="T9" t="n">
-        <v>1074.2</v>
+        <v>1278</v>
       </c>
       <c r="U9" t="n">
-        <v>1074.7</v>
+        <v>1280.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1010.283333333333</v>
+        <v>1157.184970092773</v>
       </c>
       <c r="W9" t="n">
-        <v>15.44991409719159</v>
+        <v>-8.482500372270351</v>
       </c>
       <c r="X9" t="n">
-        <v>2.798912882849386</v>
+        <v>-8.492960901690422</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.65100121434221</v>
+        <v>0.01046052942007059</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5978825348422</v>
+        <v>-11.81469275014517</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.008849557522123908</v>
+        <v>-0.04029304029304026</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1417624521072797</v>
+        <v>0.2880115114876634</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.05342537180250728</v>
+        <v>-0.06836277997698026</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.163149838735737</v>
+        <v>0.2690187479364008</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1097244669332297</v>
+        <v>-0.3373815279133811</v>
       </c>
       <c r="AG9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="AI9" t="b">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>1116.79</v>
+        <v>1311.32</v>
       </c>
     </row>
     <row r="10">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1835,7 +1835,7 @@
         <v>153.5</v>
       </c>
       <c r="R10" t="n">
-        <v>111348972</v>
+        <v>110638385</v>
       </c>
       <c r="S10" t="n">
         <v>156.9</v>
@@ -1871,13 +1871,13 @@
         <v>-0.08429881578813225</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1361934164888474</v>
+        <v>0.1526994910852908</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.1056862024165895</v>
+        <v>-0.1032915793393948</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.241879618905437</v>
+        <v>0.2559910704246856</v>
       </c>
       <c r="AG10" t="n">
         <v>90</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1977,7 +1977,7 @@
         <v>7925</v>
       </c>
       <c r="R11" t="n">
-        <v>1061923</v>
+        <v>979594</v>
       </c>
       <c r="S11" t="n">
         <v>8165</v>
@@ -2013,13 +2013,13 @@
         <v>0.5724206349206349</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2729636703413956</v>
+        <v>0.2894697449378389</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.5510332482921776</v>
+        <v>0.5534278713693723</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.278069577950782</v>
+        <v>-0.2639581264315334</v>
       </c>
       <c r="AG11" t="n">
         <v>100</v>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -2119,7 +2119,7 @@
         <v>294.5</v>
       </c>
       <c r="R12" t="n">
-        <v>29691511</v>
+        <v>28180195</v>
       </c>
       <c r="S12" t="n">
         <v>305.6</v>
@@ -2155,13 +2155,13 @@
         <v>-0.07341519200743485</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.04616492646035741</v>
+        <v>0.06267100105680079</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.09480257863589214</v>
+        <v>-0.09240795555869741</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1409675050962496</v>
+        <v>0.1550789566154982</v>
       </c>
       <c r="AG12" t="n">
         <v>78</v>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.6</v>
+        <v>47.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2261,7 +2261,7 @@
         <v>1165</v>
       </c>
       <c r="R13" t="n">
-        <v>10788550</v>
+        <v>10469722</v>
       </c>
       <c r="S13" t="n">
         <v>1130</v>
@@ -2297,13 +2297,13 @@
         <v>0.2047322672366025</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.004973735269166113</v>
+        <v>0.02147980986560949</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1833448806081452</v>
+        <v>0.18573950368534</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1783711453389791</v>
+        <v>-0.1642596938197305</v>
       </c>
       <c r="AG13" t="n">
         <v>66</v>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2362,96 +2362,96 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7389000</v>
+        <v>168900</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7320000</v>
+        <v>168900</v>
       </c>
       <c r="N14" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.009426229508196722</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1835</v>
+        <v>19395</v>
       </c>
       <c r="Q14" t="n">
-        <v>1835</v>
+        <v>19395</v>
       </c>
       <c r="R14" t="n">
-        <v>13773563</v>
+        <v>229955</v>
       </c>
       <c r="S14" t="n">
-        <v>1884</v>
+        <v>20047</v>
       </c>
       <c r="T14" t="n">
-        <v>1780.25</v>
+        <v>18570.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1780</v>
+        <v>18382</v>
       </c>
       <c r="V14" t="n">
-        <v>1777</v>
+        <v>16246.68181966146</v>
       </c>
       <c r="W14" t="n">
-        <v>33.07665985345807</v>
+        <v>681.6505405317366</v>
       </c>
       <c r="X14" t="n">
-        <v>11.58825139616999</v>
+        <v>661.1887770537031</v>
       </c>
       <c r="Y14" t="n">
-        <v>21.48840845728808</v>
+        <v>20.4617634780335</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.30151505953038</v>
+        <v>124.9044452154969</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.002732240437158362</v>
+        <v>0.2408829174664107</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.1156626506024097</v>
+        <v>0.2357081148782567</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.04184357384322501</v>
+        <v>0.2128131777824707</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.137050037230867</v>
+        <v>0.2167153513269942</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09520646338764194</v>
+        <v>-0.003902173544523491</v>
       </c>
       <c r="AG14" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="AH14" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2513,15 +2513,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>168900</v>
+        <v>476000</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>168900</v>
+        <v>476000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2539,61 +2539,61 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19395</v>
+        <v>1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>19395</v>
+        <v>1585</v>
       </c>
       <c r="R15" t="n">
-        <v>258047</v>
+        <v>4986784</v>
       </c>
       <c r="S15" t="n">
-        <v>20047</v>
+        <v>1563</v>
       </c>
       <c r="T15" t="n">
-        <v>18570.25</v>
+        <v>1342</v>
       </c>
       <c r="U15" t="n">
-        <v>18382</v>
+        <v>1326</v>
       </c>
       <c r="V15" t="n">
-        <v>16246.68181966146</v>
+        <v>1192.783333333333</v>
       </c>
       <c r="W15" t="n">
-        <v>681.6505405317366</v>
+        <v>91.03166828477333</v>
       </c>
       <c r="X15" t="n">
-        <v>661.1887770537031</v>
+        <v>66.63569507951343</v>
       </c>
       <c r="Y15" t="n">
-        <v>20.4617634780335</v>
+        <v>24.39597320525991</v>
       </c>
       <c r="Z15" t="n">
-        <v>124.9044452154969</v>
+        <v>26.89554554167307</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2408829174664107</v>
+        <v>0.2529644268774704</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2357081148782567</v>
+        <v>0.1485507246376812</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1963071031860273</v>
+        <v>0.2248946871935305</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2143207282497994</v>
+        <v>0.1295579610864186</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01801362506377213</v>
+        <v>0.09533672610711186</v>
       </c>
       <c r="AG15" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AI15" t="b">
         <v>1</v>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>46.6</v>
+        <v>45.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2655,15 +2655,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>476000</v>
+        <v>5086000</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>476000</v>
+        <v>5086000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2681,61 +2681,61 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1585</v>
+        <v>4910</v>
       </c>
       <c r="Q16" t="n">
-        <v>1585</v>
+        <v>4910</v>
       </c>
       <c r="R16" t="n">
-        <v>5079374</v>
+        <v>11051455</v>
       </c>
       <c r="S16" t="n">
-        <v>1563</v>
+        <v>5114</v>
       </c>
       <c r="T16" t="n">
-        <v>1342</v>
+        <v>4648.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1326</v>
+        <v>4602.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1192.783333333333</v>
+        <v>4087.508333333333</v>
       </c>
       <c r="W16" t="n">
-        <v>91.03166828477333</v>
+        <v>214.5734033226527</v>
       </c>
       <c r="X16" t="n">
-        <v>66.63569507951343</v>
+        <v>191.9008320589306</v>
       </c>
       <c r="Y16" t="n">
-        <v>24.39597320525991</v>
+        <v>22.67257126372203</v>
       </c>
       <c r="Z16" t="n">
-        <v>26.89554554167307</v>
+        <v>61.15996141600954</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2529644268774704</v>
+        <v>0.232120451693852</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1485507246376812</v>
+        <v>0.177434319883583</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.2083886125970871</v>
+        <v>0.204050712009912</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1271633380092239</v>
+        <v>0.1584415563323205</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.08122527458786322</v>
+        <v>0.0456091556775915</v>
       </c>
       <c r="AG16" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AI16" t="b">
         <v>1</v>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>45.8</v>
+        <v>43.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heavy Buy</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6151000</v>
+        <v>11464000</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -2814,76 +2814,76 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5886000</v>
+        <v>11464000</v>
       </c>
       <c r="N17" t="n">
-        <v>265000</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04502208630648998</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1485</v>
+        <v>2475</v>
       </c>
       <c r="Q17" t="n">
-        <v>1485</v>
+        <v>2475</v>
       </c>
       <c r="R17" t="n">
-        <v>5912851</v>
+        <v>24637205</v>
       </c>
       <c r="S17" t="n">
-        <v>1463</v>
+        <v>2478</v>
       </c>
       <c r="T17" t="n">
-        <v>1401.25</v>
+        <v>2430.986926269531</v>
       </c>
       <c r="U17" t="n">
-        <v>1401.5</v>
+        <v>2427.881787109375</v>
       </c>
       <c r="V17" t="n">
-        <v>1412.416666666667</v>
+        <v>2395.413081868489</v>
       </c>
       <c r="W17" t="n">
-        <v>16.75624182819433</v>
+        <v>19.99968999227895</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.188644010547854</v>
+        <v>14.22732978166766</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.94488583874219</v>
+        <v>5.772360210611286</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.0215381971915</v>
+        <v>7.452008552691755</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.003355704697986628</v>
+        <v>0.02573784857921413</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1703910614525139</v>
+        <v>0.01524967584937387</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.04793151897837</v>
+        <v>-0.002331891104725869</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.1917784480809712</v>
+        <v>-0.003743087701888692</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1438469291026012</v>
+        <v>0.001411196597162823</v>
       </c>
       <c r="AG17" t="n">
-        <v>46</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
       </c>
       <c r="AJ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK17" t="b">
         <v>1</v>
@@ -2902,8 +2902,10 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP17" t="n">
-        <v>1346.84</v>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Already Up</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2914,12 +2916,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2928,7 +2930,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>45.6</v>
+        <v>41.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2937,15 +2939,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5086000</v>
+        <v>251000</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
@@ -2954,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5086000</v>
+        <v>251000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2963,73 +2965,73 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4910</v>
+        <v>3140</v>
       </c>
       <c r="Q18" t="n">
-        <v>4910</v>
+        <v>3140</v>
       </c>
       <c r="R18" t="n">
-        <v>13191812</v>
+        <v>692318</v>
       </c>
       <c r="S18" t="n">
-        <v>5114</v>
+        <v>3422</v>
       </c>
       <c r="T18" t="n">
-        <v>4648.5</v>
+        <v>3382.25</v>
       </c>
       <c r="U18" t="n">
-        <v>4602.25</v>
+        <v>3359.25</v>
       </c>
       <c r="V18" t="n">
-        <v>4087.508333333333</v>
+        <v>2937.38525390625</v>
       </c>
       <c r="W18" t="n">
-        <v>214.5734033226527</v>
+        <v>38.22946124147575</v>
       </c>
       <c r="X18" t="n">
-        <v>191.9008320589305</v>
+        <v>96.27406748320537</v>
       </c>
       <c r="Y18" t="n">
-        <v>22.6725712637222</v>
+        <v>-58.04460624172962</v>
       </c>
       <c r="Z18" t="n">
-        <v>61.15996141600971</v>
+        <v>-31.68615021447238</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.232120451693852</v>
+        <v>0.1716417910447761</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.177434319883583</v>
+        <v>-0.0491159431872682</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1875446374134686</v>
+        <v>0.1435720513608361</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1560469332551258</v>
+        <v>-0.06810870673853076</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03149770415834285</v>
+        <v>0.2116807580993668</v>
       </c>
       <c r="AG18" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="b">
         <v>0</v>
@@ -3037,11 +3039,7 @@
       <c r="AN18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3056,12 +3054,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3070,7 +3068,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>43.2</v>
+        <v>41.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3079,24 +3077,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>11464000</v>
+        <v>1673000</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>11464000</v>
+        <v>1673000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3105,61 +3103,61 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2475</v>
+        <v>2515</v>
       </c>
       <c r="Q19" t="n">
-        <v>2475</v>
+        <v>2515</v>
       </c>
       <c r="R19" t="n">
-        <v>25532143</v>
+        <v>1014163</v>
       </c>
       <c r="S19" t="n">
-        <v>2478</v>
+        <v>2512</v>
       </c>
       <c r="T19" t="n">
-        <v>2430.986926269531</v>
+        <v>2261.5</v>
       </c>
       <c r="U19" t="n">
-        <v>2427.881787109375</v>
+        <v>2253</v>
       </c>
       <c r="V19" t="n">
-        <v>2395.413081868489</v>
+        <v>1821.885439046224</v>
       </c>
       <c r="W19" t="n">
-        <v>19.99968999071962</v>
+        <v>123.0591685427753</v>
       </c>
       <c r="X19" t="n">
-        <v>14.22732977855515</v>
+        <v>93.50206457801306</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.772360212164466</v>
+        <v>29.55710396476223</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.452008554438146</v>
+        <v>36.56152320720935</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.02573784857921413</v>
+        <v>0.07249466950959493</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01524967584937387</v>
+        <v>0.5537346219685011</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.01883796570116925</v>
+        <v>0.04442492982565494</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.006137710779083427</v>
+        <v>0.5347418584172385</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.01270025492208582</v>
+        <v>-0.4903169285915836</v>
       </c>
       <c r="AG19" t="n">
-        <v>56.00000000000001</v>
+        <v>72</v>
       </c>
       <c r="AH19" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3198,12 +3196,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3212,7 +3210,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3221,15 +3219,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>251000</v>
+        <v>1000</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
@@ -3238,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>251000</v>
+        <v>1000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3247,73 +3245,73 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3140</v>
+        <v>104.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3140</v>
+        <v>104.5</v>
       </c>
       <c r="R20" t="n">
-        <v>768231</v>
+        <v>52740037</v>
       </c>
       <c r="S20" t="n">
-        <v>3422</v>
+        <v>106.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3382.25</v>
+        <v>93.65999946594238</v>
       </c>
       <c r="U20" t="n">
-        <v>3359.25</v>
+        <v>92.95999946594239</v>
       </c>
       <c r="V20" t="n">
-        <v>2937.38525390625</v>
+        <v>94.34833323160807</v>
       </c>
       <c r="W20" t="n">
-        <v>38.22946124147575</v>
+        <v>4.790189329418197</v>
       </c>
       <c r="X20" t="n">
-        <v>96.27406748320537</v>
+        <v>2.493172617357349</v>
       </c>
       <c r="Y20" t="n">
-        <v>-58.04460624172962</v>
+        <v>2.297016712060849</v>
       </c>
       <c r="Z20" t="n">
-        <v>-31.68615021447238</v>
+        <v>3.020558977502503</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1716417910447761</v>
+        <v>0.1546961325966851</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0491159431872682</v>
+        <v>-0.004761904761904745</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1270659767643927</v>
+        <v>0.1266263929127451</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.07050332981572549</v>
+        <v>-0.0237546683131673</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1975693065801182</v>
+        <v>0.1503810612259124</v>
       </c>
       <c r="AG20" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AH20" t="n">
-        <v>50</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="AI20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="b">
         <v>0</v>
@@ -3321,7 +3319,11 @@
       <c r="AN20" t="b">
         <v>0</v>
       </c>
-      <c r="AO20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
+      </c>
       <c r="AP20" t="inlineStr">
         <is>
           <t>Already Up</t>
@@ -3336,12 +3338,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3350,96 +3352,96 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>41.2</v>
+        <v>40.59999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Heavy Sell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1673000</v>
+        <v>12526000</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1673000</v>
+        <v>12966000</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-440000</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.03393490667900663</v>
       </c>
       <c r="P21" t="n">
-        <v>2515</v>
+        <v>687</v>
       </c>
       <c r="Q21" t="n">
-        <v>2515</v>
+        <v>687</v>
       </c>
       <c r="R21" t="n">
-        <v>1045457</v>
+        <v>13784732</v>
       </c>
       <c r="S21" t="n">
-        <v>2512</v>
+        <v>687</v>
       </c>
       <c r="T21" t="n">
-        <v>2261.5</v>
+        <v>630.15</v>
       </c>
       <c r="U21" t="n">
-        <v>2253</v>
+        <v>626.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1821.885439046224</v>
+        <v>619.0166666666667</v>
       </c>
       <c r="W21" t="n">
-        <v>123.0591685427753</v>
+        <v>22.3859817273509</v>
       </c>
       <c r="X21" t="n">
-        <v>93.50206457801306</v>
+        <v>13.93385791776243</v>
       </c>
       <c r="Y21" t="n">
-        <v>29.55710396476223</v>
+        <v>8.452123809588464</v>
       </c>
       <c r="Z21" t="n">
-        <v>36.56152320720935</v>
+        <v>10.42840216651905</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.07249466950959493</v>
+        <v>0.106280193236715</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5537346219685011</v>
+        <v>0.007331378299120228</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.02791885522921156</v>
+        <v>0.07821045355277501</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.5323472353400438</v>
+        <v>-0.01166138525214233</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.5044283801108322</v>
+        <v>0.08987183880491734</v>
       </c>
       <c r="AG21" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="AI21" t="b">
         <v>1</v>
@@ -3478,12 +3480,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3492,7 +3494,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>38.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3501,24 +3503,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1000</v>
+        <v>7389000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3527,61 +3529,61 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>104.5</v>
+        <v>1835</v>
       </c>
       <c r="Q22" t="n">
-        <v>104.5</v>
+        <v>1835</v>
       </c>
       <c r="R22" t="n">
-        <v>53107330</v>
+        <v>12874206</v>
       </c>
       <c r="S22" t="n">
-        <v>106.4</v>
+        <v>1884</v>
       </c>
       <c r="T22" t="n">
-        <v>93.65999946594238</v>
+        <v>1780.25</v>
       </c>
       <c r="U22" t="n">
-        <v>92.95999946594239</v>
+        <v>1780</v>
       </c>
       <c r="V22" t="n">
-        <v>94.34833323160807</v>
+        <v>1777</v>
       </c>
       <c r="W22" t="n">
-        <v>4.790189329418197</v>
+        <v>33.07665985345807</v>
       </c>
       <c r="X22" t="n">
-        <v>2.493172617357349</v>
+        <v>11.58825139616999</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.297016712060849</v>
+        <v>21.48840845728808</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.020558977502503</v>
+        <v>30.30151505953038</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1546961325966851</v>
+        <v>0.002732240437158362</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.004761904761904745</v>
+        <v>-0.1156626506024097</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1101203183163018</v>
+        <v>-0.02533749924678164</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.02614929139036204</v>
+        <v>-0.1346554141536722</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1362696097066638</v>
+        <v>0.1093179149068906</v>
       </c>
       <c r="AG22" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AH22" t="n">
-        <v>57.99999999999999</v>
+        <v>38</v>
       </c>
       <c r="AI22" t="b">
         <v>1</v>
@@ -3620,12 +3622,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3634,96 +3636,96 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>40.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12966000</v>
+        <v>1000</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>13966000</v>
+        <v>1000</v>
       </c>
       <c r="N23" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.07160246312473149</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>687</v>
+        <v>2185</v>
       </c>
       <c r="Q23" t="n">
-        <v>687</v>
+        <v>2185</v>
       </c>
       <c r="R23" t="n">
-        <v>14223216</v>
+        <v>2293204</v>
       </c>
       <c r="S23" t="n">
-        <v>687</v>
+        <v>2324</v>
       </c>
       <c r="T23" t="n">
-        <v>630.15</v>
+        <v>2174.25</v>
       </c>
       <c r="U23" t="n">
-        <v>626.85</v>
+        <v>2165.5</v>
       </c>
       <c r="V23" t="n">
-        <v>619.0166666666667</v>
+        <v>2072.583333333333</v>
       </c>
       <c r="W23" t="n">
-        <v>22.3859817273509</v>
+        <v>44.31469793968517</v>
       </c>
       <c r="X23" t="n">
-        <v>13.93385791776243</v>
+        <v>43.49191492007922</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.452123809588464</v>
+        <v>0.8227830196059571</v>
       </c>
       <c r="Z23" t="n">
-        <v>10.42840216651905</v>
+        <v>18.1601972229389</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.106280193236715</v>
+        <v>0.08706467661691542</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.007331378299120228</v>
+        <v>-0.03532008830022071</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.06170437895633163</v>
+        <v>0.05899493693297542</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.01405600832933707</v>
+        <v>-0.05431285185148327</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0757603872856687</v>
+        <v>0.1133077887844587</v>
       </c>
       <c r="AG23" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AI23" t="b">
         <v>1</v>
@@ -3762,12 +3764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3776,7 +3778,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3785,7 +3787,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3793,7 +3795,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -3811,84 +3813,82 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2185</v>
+        <v>95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2185</v>
+        <v>95</v>
       </c>
       <c r="R24" t="n">
-        <v>2400440</v>
+        <v>4419115</v>
       </c>
       <c r="S24" t="n">
-        <v>2324</v>
+        <v>99.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2174.25</v>
+        <v>99.41500015258789</v>
       </c>
       <c r="U24" t="n">
-        <v>2165.5</v>
+        <v>99.27000007629394</v>
       </c>
       <c r="V24" t="n">
-        <v>2072.583333333333</v>
+        <v>90.17666676839193</v>
       </c>
       <c r="W24" t="n">
-        <v>44.31469793968517</v>
+        <v>0.5228938906103764</v>
       </c>
       <c r="X24" t="n">
-        <v>43.49191492007922</v>
+        <v>1.591292314344823</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.8227830196059571</v>
+        <v>-1.068398423734447</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.1601972229389</v>
+        <v>-0.5503008803853495</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.08706467661691542</v>
+        <v>0.03148753066150989</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.03532008830022071</v>
+        <v>0.2786002166624737</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.04248886233653204</v>
+        <v>0.00341779097756989</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.056707474928678</v>
+        <v>0.2596074531112111</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.09919633726521004</v>
+        <v>-0.2561896621336412</v>
       </c>
       <c r="AG24" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="AH24" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="b">
         <v>0</v>
       </c>
       <c r="AN24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>107.16</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -3904,12 +3904,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37.59999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3927,15 +3927,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3953,82 +3953,84 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>95</v>
+        <v>175.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>95</v>
+        <v>175.5</v>
       </c>
       <c r="R25" t="n">
-        <v>4489109</v>
+        <v>20459060</v>
       </c>
       <c r="S25" t="n">
-        <v>99.8</v>
+        <v>172.4</v>
       </c>
       <c r="T25" t="n">
-        <v>99.41500015258789</v>
+        <v>160.475</v>
       </c>
       <c r="U25" t="n">
-        <v>99.27000007629394</v>
+        <v>159.4</v>
       </c>
       <c r="V25" t="n">
-        <v>90.17666676839193</v>
+        <v>154.2166666666667</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5228938906103764</v>
+        <v>6.314317891986974</v>
       </c>
       <c r="X25" t="n">
-        <v>1.591292314344823</v>
+        <v>5.170831844702452</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.068398423734447</v>
+        <v>1.143486047284522</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.5503008803853495</v>
+        <v>1.281645156583237</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.03148753066150989</v>
+        <v>0.1396103896103895</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.2786002166624737</v>
+        <v>-0.1521739130434783</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01308828361887349</v>
+        <v>0.1115406499264495</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2572128300340164</v>
+        <v>-0.1711666765947408</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.2703011136528899</v>
+        <v>0.2827073265211903</v>
       </c>
       <c r="AG25" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="AH25" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="b">
         <v>0</v>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>107.16</v>
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4044,12 +4046,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4058,7 +4060,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4067,24 +4069,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5000</v>
+        <v>6151000</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>5000</v>
+        <v>6151000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -4093,67 +4095,67 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>175.5</v>
+        <v>1485</v>
       </c>
       <c r="Q26" t="n">
-        <v>175.5</v>
+        <v>1485</v>
       </c>
       <c r="R26" t="n">
-        <v>20579836</v>
+        <v>5656430</v>
       </c>
       <c r="S26" t="n">
-        <v>172.4</v>
+        <v>1463</v>
       </c>
       <c r="T26" t="n">
-        <v>160.475</v>
+        <v>1401.25</v>
       </c>
       <c r="U26" t="n">
-        <v>159.4</v>
+        <v>1401.5</v>
       </c>
       <c r="V26" t="n">
-        <v>154.2166666666667</v>
+        <v>1412.416666666667</v>
       </c>
       <c r="W26" t="n">
-        <v>6.314317891986974</v>
+        <v>16.75624182819433</v>
       </c>
       <c r="X26" t="n">
-        <v>5.170831844702452</v>
+        <v>-2.188644010547854</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.143486047284522</v>
+        <v>18.94488583874219</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.281645156583237</v>
+        <v>19.0215381971915</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.1396103896103895</v>
+        <v>-0.003355704697986628</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.1521739130434783</v>
+        <v>-0.1703910614525139</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.09503457533000614</v>
+        <v>-0.03142544438192663</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.1735612996719356</v>
+        <v>-0.1893838250037765</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.2685958750019417</v>
+        <v>0.1579583806218499</v>
       </c>
       <c r="AG26" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="AH26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="b">
         <v>1</v>
       </c>
       <c r="AJ26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="b">
         <v>1</v>
@@ -4172,10 +4174,8 @@
           <t>Already &gt; 0</t>
         </is>
       </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>Already Up</t>
-        </is>
+      <c r="AP26" t="n">
+        <v>1346.84</v>
       </c>
     </row>
     <row r="27">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -4241,7 +4241,7 @@
         <v>3400</v>
       </c>
       <c r="R27" t="n">
-        <v>3706504</v>
+        <v>3431524</v>
       </c>
       <c r="S27" t="n">
         <v>3446</v>
@@ -4277,13 +4277,13 @@
         <v>0.2391919732279579</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.03267105237562151</v>
+        <v>-0.01616497777917814</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2178045865995006</v>
+        <v>0.2201992096766954</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.2504756389751222</v>
+        <v>-0.2363641874558735</v>
       </c>
       <c r="AG27" t="n">
         <v>50</v>
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4383,7 +4383,7 @@
         <v>241.5</v>
       </c>
       <c r="R28" t="n">
-        <v>10617645</v>
+        <v>10373702</v>
       </c>
       <c r="S28" t="n">
         <v>260</v>
@@ -4419,13 +4419,13 @@
         <v>-0.02226720647773284</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01691623981229817</v>
+        <v>-0.0004101652158547964</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.04365459310619013</v>
+        <v>-0.0412599700289954</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.02673835329389196</v>
+        <v>0.0408498048131406</v>
       </c>
       <c r="AG28" t="n">
         <v>57.99999999999999</v>
@@ -4482,7 +4482,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>32.59999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -4523,7 +4523,7 @@
         <v>227</v>
       </c>
       <c r="R29" t="n">
-        <v>1227422</v>
+        <v>1194459</v>
       </c>
       <c r="S29" t="n">
         <v>228.5</v>
@@ -4559,13 +4559,13 @@
         <v>-0.1863799283154122</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.01123813920798877</v>
+        <v>0.02774421380443215</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.2077673149438695</v>
+        <v>-0.2053726918666747</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2190054541518582</v>
+        <v>0.2331169056711069</v>
       </c>
       <c r="AG29" t="n">
         <v>68</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4663,7 +4663,7 @@
         <v>336.5</v>
       </c>
       <c r="R30" t="n">
-        <v>9816683</v>
+        <v>9674015</v>
       </c>
       <c r="S30" t="n">
         <v>340.6</v>
@@ -4699,13 +4699,13 @@
         <v>-0.0693204989110987</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.03254573909241354</v>
+        <v>-0.01603966449597016</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.090707885539556</v>
+        <v>-0.08831326246236126</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.05816214644714246</v>
+        <v>0.0722735979663911</v>
       </c>
       <c r="AG30" t="n">
         <v>52</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4803,7 +4803,7 @@
         <v>5185</v>
       </c>
       <c r="R31" t="n">
-        <v>1124797</v>
+        <v>976210</v>
       </c>
       <c r="S31" t="n">
         <v>5412</v>
@@ -4839,13 +4839,13 @@
         <v>-0.2950246126757454</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01376070493644699</v>
+        <v>0.002745369659996388</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.3164119993042027</v>
+        <v>-0.314017376227008</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.3026512943677557</v>
+        <v>0.3167627458870044</v>
       </c>
       <c r="AG31" t="n">
         <v>60</v>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4943,7 +4943,7 @@
         <v>250.5</v>
       </c>
       <c r="R32" t="n">
-        <v>30593394</v>
+        <v>30194485</v>
       </c>
       <c r="S32" t="n">
         <v>252</v>
@@ -4979,13 +4979,13 @@
         <v>0.04158004158004158</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.05445723720528461</v>
+        <v>-0.03795116260884124</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.02019265495158429</v>
+        <v>0.02258727802877902</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.0746498921568689</v>
+        <v>-0.06053844063762026</v>
       </c>
       <c r="AG32" t="n">
         <v>40</v>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -5083,7 +5083,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="R33" t="n">
-        <v>36555448</v>
+        <v>36481292</v>
       </c>
       <c r="S33" t="n">
         <v>18.67999954223633</v>
@@ -5119,13 +5119,13 @@
         <v>-6.279652717955386e-05</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.05769917438601746</v>
+        <v>-0.04119309978957408</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.02145018315563685</v>
+        <v>-0.01905556007844211</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.03624899123038061</v>
+        <v>-0.02213753971113197</v>
       </c>
       <c r="AG33" t="n">
         <v>38</v>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -5223,7 +5223,7 @@
         <v>78.09999847412109</v>
       </c>
       <c r="R34" t="n">
-        <v>1216944</v>
+        <v>1207246</v>
       </c>
       <c r="S34" t="n">
         <v>78.19999847412109</v>
@@ -5259,13 +5259,13 @@
         <v>-0.1085829664639786</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.04967137511960507</v>
+        <v>-0.03316530052316169</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.1299703530924359</v>
+        <v>-0.1275757300152411</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.08029897797283081</v>
+        <v>0.09441042949207945</v>
       </c>
       <c r="AG34" t="n">
         <v>44</v>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -5363,7 +5363,7 @@
         <v>548</v>
       </c>
       <c r="R35" t="n">
-        <v>41035274</v>
+        <v>39224107</v>
       </c>
       <c r="S35" t="n">
         <v>565.8</v>
@@ -5399,13 +5399,13 @@
         <v>-0.4755980861244019</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.1266528662066815</v>
+        <v>-0.1101467916102381</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.4969854727528592</v>
+        <v>-0.4945908496756645</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.3703326065461777</v>
+        <v>0.3844440580654264</v>
       </c>
       <c r="AG35" t="n">
         <v>22</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5503,7 +5503,7 @@
         <v>506</v>
       </c>
       <c r="R36" t="n">
-        <v>24890762</v>
+        <v>24327412</v>
       </c>
       <c r="S36" t="n">
         <v>507.4</v>
@@ -5539,13 +5539,13 @@
         <v>0.2396246362848151</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1075387772433464</v>
+        <v>-0.091032702646903</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.2182372496563578</v>
+        <v>0.2206318727335526</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.3257760268997042</v>
+        <v>-0.3116645753804556</v>
       </c>
       <c r="AG36" t="n">
         <v>26</v>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5643,7 +5643,7 @@
         <v>567</v>
       </c>
       <c r="R37" t="n">
-        <v>951235</v>
+        <v>925273</v>
       </c>
       <c r="S37" t="n">
         <v>588.6</v>
@@ -5679,13 +5679,13 @@
         <v>0.2164972861756815</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1150676175590719</v>
+        <v>-0.09856154296262853</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1951098995472242</v>
+        <v>0.197504522624419</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.3101775171062962</v>
+        <v>-0.2960660655870475</v>
       </c>
       <c r="AG37" t="n">
         <v>24</v>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5781,7 +5781,7 @@
         <v>226</v>
       </c>
       <c r="R38" t="n">
-        <v>10020552</v>
+        <v>9861253</v>
       </c>
       <c r="S38" t="n">
         <v>223.3</v>
@@ -5817,13 +5817,13 @@
         <v>-0.01525054466230935</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.1068164781807983</v>
+        <v>-0.09031040358435494</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.03663793129076665</v>
+        <v>-0.03424330821357191</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.07017854689003167</v>
+        <v>-0.05606709537078303</v>
       </c>
       <c r="AG38" t="n">
         <v>28</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5919,7 +5919,7 @@
         <v>569</v>
       </c>
       <c r="R39" t="n">
-        <v>232543</v>
+        <v>220236</v>
       </c>
       <c r="S39" t="n">
         <v>570.8</v>
@@ -5934,16 +5934,16 @@
         <v>578.7163747151693</v>
       </c>
       <c r="W39" t="n">
-        <v>2.905234999841696</v>
+        <v>2.905234999840673</v>
       </c>
       <c r="X39" t="n">
-        <v>-1.264685839276776</v>
+        <v>-1.264685839278743</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.169920839118472</v>
+        <v>4.169920839119415</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.879444149136265</v>
+        <v>4.879444149137329</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -5955,13 +5955,13 @@
         <v>-0.1164863388211188</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.07026074578723274</v>
+        <v>-0.05375467119078936</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.1378737254495761</v>
+        <v>-0.1354791023723814</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.06761297966234336</v>
+        <v>0.08172443118159201</v>
       </c>
       <c r="AG39" t="n">
         <v>34</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -6059,7 +6059,7 @@
         <v>83.09999847412109</v>
       </c>
       <c r="R40" t="n">
-        <v>1035348</v>
+        <v>1025747</v>
       </c>
       <c r="S40" t="n">
         <v>83.14000091552734</v>
@@ -6095,13 +6095,13 @@
         <v>-0.2111138094373449</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.06346599765428373</v>
+        <v>-0.04695992305784036</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.2325011960658022</v>
+        <v>-0.2301065729886075</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.1690351984115185</v>
+        <v>0.1831466499307671</v>
       </c>
       <c r="AG40" t="n">
         <v>36</v>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -6199,7 +6199,7 @@
         <v>1810</v>
       </c>
       <c r="R41" t="n">
-        <v>4153316</v>
+        <v>3767665</v>
       </c>
       <c r="S41" t="n">
         <v>1870</v>
@@ -6235,13 +6235,13 @@
         <v>-0.3329699668417579</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.1928111083980304</v>
+        <v>-0.176305033801587</v>
       </c>
       <c r="AE41" t="n">
-        <v>-0.3543573534702152</v>
+        <v>-0.3519627303930205</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.1615462450721848</v>
+        <v>0.1756576965914335</v>
       </c>
       <c r="AG41" t="n">
         <v>4</v>
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6339,7 +6339,7 @@
         <v>6020</v>
       </c>
       <c r="R42" t="n">
-        <v>1778124</v>
+        <v>1514869</v>
       </c>
       <c r="S42" t="n">
         <v>6252</v>
@@ -6354,16 +6354,16 @@
         <v>5252.736177571614</v>
       </c>
       <c r="W42" t="n">
-        <v>-54.19210189352088</v>
+        <v>-54.1921018935227</v>
       </c>
       <c r="X42" t="n">
-        <v>41.14392880557755</v>
+        <v>41.14392880557538</v>
       </c>
       <c r="Y42" t="n">
-        <v>-95.33603069909844</v>
+        <v>-95.33603069909807</v>
       </c>
       <c r="Z42" t="n">
-        <v>-88.88242318529913</v>
+        <v>-88.88242318529869</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -6375,13 +6375,13 @@
         <v>0.4361668978356548</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1924880577340281</v>
+        <v>-0.1759819831375847</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.4147795112071975</v>
+        <v>0.4171741342843922</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.6072675689412256</v>
+        <v>-0.5931561174219769</v>
       </c>
       <c r="AG42" t="n">
         <v>6</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -6477,7 +6477,7 @@
         <v>945</v>
       </c>
       <c r="R43" t="n">
-        <v>9147468</v>
+        <v>8858935</v>
       </c>
       <c r="S43" t="n">
         <v>949</v>
@@ -6513,13 +6513,13 @@
         <v>-0.2441006881505237</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.07235359205816116</v>
+        <v>-0.05584751746171779</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.265488074778981</v>
+        <v>-0.2630934517017862</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.1931344827208198</v>
+        <v>0.2072459342400684</v>
       </c>
       <c r="AG43" t="n">
         <v>32</v>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6585,15 +6585,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1000</v>
+        <v>4812561</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6602,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1000</v>
+        <v>4812561</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6611,61 +6611,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>498</v>
+        <v>2100</v>
       </c>
       <c r="Q44" t="n">
-        <v>498</v>
+        <v>2100</v>
       </c>
       <c r="R44" t="n">
-        <v>13754919</v>
+        <v>1491509</v>
       </c>
       <c r="S44" t="n">
-        <v>497.8</v>
+        <v>2117</v>
       </c>
       <c r="T44" t="n">
-        <v>504.15</v>
+        <v>2303.181958007813</v>
       </c>
       <c r="U44" t="n">
-        <v>506.4</v>
+        <v>2318.874145507812</v>
       </c>
       <c r="V44" t="n">
-        <v>444.9723617553711</v>
+        <v>2049.523036702474</v>
       </c>
       <c r="W44" t="n">
-        <v>4.732626012677144</v>
+        <v>-53.14595567825836</v>
       </c>
       <c r="X44" t="n">
-        <v>8.169927233199608</v>
+        <v>-26.07044988566617</v>
       </c>
       <c r="Y44" t="n">
-        <v>-3.437301220522464</v>
+        <v>-27.07550579259219</v>
       </c>
       <c r="Z44" t="n">
-        <v>-3.543413592575728</v>
+        <v>-32.71960656973074</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.08287292817679559</v>
+        <v>-0.130018254081276</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.1520691926783012</v>
+        <v>0.1897186762636975</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.127448742457179</v>
+        <v>-0.158087993765216</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.1734565793067585</v>
+        <v>0.170725912712435</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.04600783684957954</v>
+        <v>-0.328813906477651</v>
       </c>
       <c r="AG44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AH44" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6686,10 +6686,10 @@
         <v>1</v>
       </c>
       <c r="AO44" t="n">
-        <v>536.84</v>
+        <v>2406.6</v>
       </c>
       <c r="AP44" t="n">
-        <v>546.47</v>
+        <v>2592.52</v>
       </c>
     </row>
     <row r="45">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6749,61 +6749,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3685</v>
+        <v>498</v>
       </c>
       <c r="Q45" t="n">
-        <v>3685</v>
+        <v>498</v>
       </c>
       <c r="R45" t="n">
-        <v>1173328</v>
+        <v>13255069</v>
       </c>
       <c r="S45" t="n">
-        <v>3719</v>
+        <v>497.8</v>
       </c>
       <c r="T45" t="n">
-        <v>3806.133447265625</v>
+        <v>504.15</v>
       </c>
       <c r="U45" t="n">
-        <v>3823.557153320312</v>
+        <v>506.4</v>
       </c>
       <c r="V45" t="n">
-        <v>3722.035770670573</v>
+        <v>444.9723617553711</v>
       </c>
       <c r="W45" t="n">
-        <v>-34.62518804981619</v>
+        <v>4.732626012677144</v>
       </c>
       <c r="X45" t="n">
-        <v>-57.22502843566262</v>
+        <v>8.169927233199608</v>
       </c>
       <c r="Y45" t="n">
-        <v>22.59984038584643</v>
+        <v>-3.437301220522464</v>
       </c>
       <c r="Z45" t="n">
-        <v>22.952187296328</v>
+        <v>-3.543413592575728</v>
       </c>
       <c r="AA45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.08639552669281902</v>
+        <v>-0.08287292817679559</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.2013328334043964</v>
+        <v>-0.1520691926783012</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1309713409732024</v>
+        <v>-0.1109426678607356</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.2227202200328537</v>
+        <v>-0.1710619562295638</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.09174887905965134</v>
+        <v>0.06011928836882818</v>
       </c>
       <c r="AG45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6812,24 +6812,22 @@
         <v>0</v>
       </c>
       <c r="AK45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>536.84</v>
       </c>
       <c r="AP45" t="n">
-        <v>4170.91</v>
+        <v>546.47</v>
       </c>
     </row>
     <row r="46">
@@ -6840,12 +6838,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6854,7 +6852,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6863,88 +6861,88 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4650000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
+        <v>46</v>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3685</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3685</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1049644</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3719</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3806.133447265625</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3823.557153320312</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3722.035770670573</v>
+      </c>
+      <c r="W46" t="n">
+        <v>-34.62518804981619</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-57.22502843566262</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>22.59984038584643</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>22.952187296328</v>
+      </c>
+      <c r="AA46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-0.08639552669281902</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>-0.2013328334043964</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-0.114465266376759</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>-0.220325596955659</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.1058603305789</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH46" t="n">
         <v>16</v>
       </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>4920</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4920</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2141504</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4949</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5205</v>
-      </c>
-      <c r="U46" t="n">
-        <v>5233.5</v>
-      </c>
-      <c r="V46" t="n">
-        <v>5222.410237630208</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-122.985475366906</v>
-      </c>
-      <c r="X46" t="n">
-        <v>-121.5310149093981</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>-1.454460457507963</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>-4.91659458514917</v>
-      </c>
-      <c r="AA46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-0.1038251366120219</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>-0.1870944663359106</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>-0.1484009508924052</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>-0.2084818529643679</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0.06008090207196271</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>18</v>
-      </c>
       <c r="AI46" t="b">
         <v>0</v>
       </c>
@@ -6952,22 +6950,24 @@
         <v>0</v>
       </c>
       <c r="AK46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>4939.68</v>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP46" t="n">
-        <v>5785</v>
+        <v>4170.91</v>
       </c>
     </row>
     <row r="47">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7001,15 +7001,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1000</v>
+        <v>4650000</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1000</v>
+        <v>4650000</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7027,61 +7027,61 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1210</v>
+        <v>4920</v>
       </c>
       <c r="Q47" t="n">
-        <v>1210</v>
+        <v>4920</v>
       </c>
       <c r="R47" t="n">
-        <v>781428</v>
+        <v>1885375</v>
       </c>
       <c r="S47" t="n">
-        <v>1230</v>
+        <v>4949</v>
       </c>
       <c r="T47" t="n">
-        <v>1303.25</v>
+        <v>5205</v>
       </c>
       <c r="U47" t="n">
-        <v>1313.5</v>
+        <v>5233.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1372.252374267578</v>
+        <v>5222.410237630208</v>
       </c>
       <c r="W47" t="n">
-        <v>-41.92936277646072</v>
+        <v>-122.985475366906</v>
       </c>
       <c r="X47" t="n">
-        <v>-41.63566438906444</v>
+        <v>-121.5310149093981</v>
       </c>
       <c r="Y47" t="n">
-        <v>-0.293698387396276</v>
+        <v>-1.454460457507963</v>
       </c>
       <c r="Z47" t="n">
-        <v>-1.080270568222282</v>
+        <v>-4.91659458514917</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.1448763250883393</v>
+        <v>-0.1038251366120219</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.1417093287088268</v>
+        <v>-0.1870944663359106</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1894521393687226</v>
+        <v>-0.1318948762959619</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.1630967153372841</v>
+        <v>-0.2060872298871732</v>
       </c>
       <c r="AF47" t="n">
-        <v>-0.02635542403143853</v>
+        <v>0.07419235359121135</v>
       </c>
       <c r="AG47" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AH47" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7102,10 +7102,10 @@
         <v>1</v>
       </c>
       <c r="AO47" t="n">
-        <v>1214.84</v>
+        <v>4939.68</v>
       </c>
       <c r="AP47" t="n">
-        <v>1523.16</v>
+        <v>5785</v>
       </c>
     </row>
     <row r="48">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7139,88 +7139,88 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>93000</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
+        <v>40</v>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1210</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1210</v>
+      </c>
+      <c r="R48" t="n">
+        <v>769126</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1230</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1303.25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1313.5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1372.252374267578</v>
+      </c>
+      <c r="W48" t="n">
+        <v>-41.92936277646072</v>
+      </c>
+      <c r="X48" t="n">
+        <v>-41.63566438906444</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-0.293698387396276</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-1.080270568222282</v>
+      </c>
+      <c r="AA48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-0.1448763250883393</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-0.1417093287088268</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>-0.1729460647722793</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>-0.1607020922600894</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>-0.01224397251218989</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH48" t="n">
         <v>34</v>
       </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>93000</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>5675</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>5675</v>
-      </c>
-      <c r="R48" t="n">
-        <v>382921</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5816</v>
-      </c>
-      <c r="T48" t="n">
-        <v>6557</v>
-      </c>
-      <c r="U48" t="n">
-        <v>6585.75</v>
-      </c>
-      <c r="V48" t="n">
-        <v>6612.443286132812</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-256.1836741605221</v>
-      </c>
-      <c r="X48" t="n">
-        <v>-150.7218537727582</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>-105.4618203877638</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>-110.1137434607653</v>
-      </c>
-      <c r="AA48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>-0.09199999999999997</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>-0.4225288094645175</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>-0.1365758142803833</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>-0.4439161960929748</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.3073403818125915</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>4</v>
-      </c>
       <c r="AI48" t="b">
         <v>0</v>
       </c>
@@ -7237,11 +7237,13 @@
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1214.84</v>
+      </c>
       <c r="AP48" t="n">
-        <v>7213.42</v>
+        <v>1523.16</v>
       </c>
     </row>
     <row r="49">
@@ -7252,12 +7254,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7266,7 +7268,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7275,15 +7277,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1139000</v>
+        <v>93000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7292,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1139000</v>
+        <v>93000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7301,61 +7303,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>877</v>
+        <v>5675</v>
       </c>
       <c r="Q49" t="n">
-        <v>877</v>
+        <v>5675</v>
       </c>
       <c r="R49" t="n">
-        <v>1135012</v>
+        <v>300592</v>
       </c>
       <c r="S49" t="n">
-        <v>892.8</v>
+        <v>5816</v>
       </c>
       <c r="T49" t="n">
-        <v>916.55</v>
+        <v>6557</v>
       </c>
       <c r="U49" t="n">
-        <v>922.2</v>
+        <v>6585.75</v>
       </c>
       <c r="V49" t="n">
-        <v>1023.7</v>
+        <v>6612.443286132812</v>
       </c>
       <c r="W49" t="n">
-        <v>-17.351247899604</v>
+        <v>-256.1836741605221</v>
       </c>
       <c r="X49" t="n">
-        <v>-21.35119356877836</v>
+        <v>-150.7218537727582</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.999945669174359</v>
+        <v>-105.4618203877638</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.458706615243454</v>
+        <v>-110.1137434607653</v>
       </c>
       <c r="AA49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1141414141414141</v>
+        <v>-0.09199999999999997</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.3279693486590038</v>
+        <v>-0.4225288094645175</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1587172284217975</v>
+        <v>-0.12006973968394</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.3493567352874611</v>
+        <v>-0.4415215730157801</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.1906395068656637</v>
+        <v>0.3214518333318401</v>
       </c>
       <c r="AG49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7364,24 +7366,20 @@
         <v>0</v>
       </c>
       <c r="AK49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN49" t="b">
         <v>0</v>
       </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
-      </c>
+      <c r="AO49" t="inlineStr"/>
       <c r="AP49" t="n">
-        <v>1010.63</v>
+        <v>7213.42</v>
       </c>
     </row>
     <row r="50">
@@ -7392,12 +7390,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7406,7 +7404,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.6</v>
+        <v>14.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7415,15 +7413,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1740000</v>
+        <v>1139000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7432,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1740000</v>
+        <v>1139000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7441,61 +7439,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>171.5</v>
+        <v>877</v>
       </c>
       <c r="Q50" t="n">
-        <v>171.5</v>
+        <v>877</v>
       </c>
       <c r="R50" t="n">
-        <v>2073642</v>
+        <v>1021144</v>
       </c>
       <c r="S50" t="n">
-        <v>175.9</v>
+        <v>892.8</v>
       </c>
       <c r="T50" t="n">
-        <v>190.15</v>
+        <v>916.55</v>
       </c>
       <c r="U50" t="n">
-        <v>192.425</v>
+        <v>922.2</v>
       </c>
       <c r="V50" t="n">
-        <v>187.6991394042969</v>
+        <v>1023.7</v>
       </c>
       <c r="W50" t="n">
-        <v>-5.655320692459924</v>
+        <v>-17.351247899604</v>
       </c>
       <c r="X50" t="n">
-        <v>-4.491815215724384</v>
+        <v>-21.35119356877836</v>
       </c>
       <c r="Y50" t="n">
-        <v>-1.16350547673554</v>
+        <v>3.999945669174359</v>
       </c>
       <c r="Z50" t="n">
-        <v>-1.2357231122222</v>
+        <v>5.458706615243454</v>
       </c>
       <c r="AA50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.2096774193548387</v>
+        <v>-0.1141414141414141</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.1428375103461536</v>
+        <v>-0.3279693486590038</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2542532336352221</v>
+        <v>-0.1422111538253541</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.1642248969746108</v>
+        <v>-0.3469621122102664</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.09002833666061127</v>
+        <v>0.2047509583849123</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AH50" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7504,22 +7502,24 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>184.88</v>
+        <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP50" t="n">
-        <v>233.63</v>
+        <v>1010.63</v>
       </c>
     </row>
     <row r="51">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7544,24 +7544,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heavy Sell</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4812561</v>
+        <v>1740000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7570,70 +7570,70 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4873561</v>
+        <v>1740000</v>
       </c>
       <c r="N51" t="n">
-        <v>-61000</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.01251651513133826</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2100</v>
+        <v>171.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>2100</v>
+        <v>171.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1633262</v>
+        <v>2015119</v>
       </c>
       <c r="S51" t="n">
-        <v>2117</v>
+        <v>175.9</v>
       </c>
       <c r="T51" t="n">
-        <v>2303.181958007813</v>
+        <v>190.15</v>
       </c>
       <c r="U51" t="n">
-        <v>2318.874145507812</v>
+        <v>192.425</v>
       </c>
       <c r="V51" t="n">
-        <v>2049.523036702474</v>
+        <v>187.6991394042969</v>
       </c>
       <c r="W51" t="n">
-        <v>-53.14595567825836</v>
+        <v>-5.655320692459924</v>
       </c>
       <c r="X51" t="n">
-        <v>-26.07044988566617</v>
+        <v>-4.491815215724384</v>
       </c>
       <c r="Y51" t="n">
-        <v>-27.07550579259219</v>
+        <v>-1.16350547673554</v>
       </c>
       <c r="Z51" t="n">
-        <v>-32.71960656973074</v>
+        <v>-1.2357231122222</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.130018254081276</v>
+        <v>-0.2096774193548387</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.1897186762636975</v>
+        <v>-0.1428375103461536</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.1745940683616594</v>
+        <v>-0.2377471590387787</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.1683312896352402</v>
+        <v>-0.1618302738974161</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.3429253579968996</v>
+        <v>-0.07591688514136263</v>
       </c>
       <c r="AG51" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7654,10 +7654,10 @@
         <v>1</v>
       </c>
       <c r="AO51" t="n">
-        <v>2406.6</v>
+        <v>184.88</v>
       </c>
       <c r="AP51" t="n">
-        <v>2592.52</v>
+        <v>233.63</v>
       </c>
     </row>
   </sheetData>
